--- a/dcf/ABNB.xlsx
+++ b/dcf/ABNB.xlsx
@@ -1128,184 +1128,184 @@
     </row>
     <row r="5">
       <c r="A5" s="53" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>121.8857482706775</v>
+        <v>125.2814783802531</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>117.904365173056</v>
+        <v>121.146893136001</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>114.1044854919068</v>
+        <v>117.2013801197598</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>110.4768031247804</v>
+        <v>113.4352271352289</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>107.0125350065486</v>
+        <v>109.8392685221018</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>103.7033893109264</v>
+        <v>106.4048518997486</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>100.5415357252446</v>
+        <v>103.1238070806231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="53" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>128.6772084898287</v>
+        <v>132.0729385994043</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>124.3894210989462</v>
+        <v>127.6319490618913</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>120.2982747476128</v>
+        <v>123.3951693754658</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>116.3936511456773</v>
+        <v>119.3520751561258</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>112.6660020376549</v>
+        <v>115.4927355532081</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>109.1063144885707</v>
+        <v>111.8077770773929</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>105.7060784360015</v>
+        <v>108.28834979138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="53" t="n">
-        <v>11</v>
-      </c>
-      <c r="B7" s="54" t="n">
-        <v>135.4686687089798</v>
+        <v>11.5</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>138.8643988185554</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>130.8744770248364</v>
+        <v>134.1170049877815</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>126.4920640033188</v>
+        <v>129.5889586311718</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>122.3104991665742</v>
+        <v>125.2689231770227</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>118.3194690687613</v>
+        <v>121.1462025843145</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>114.509239666215</v>
+        <v>117.2107022550372</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>110.8706211467585</v>
+        <v>113.4528925021369</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="53" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>142.260128928131</v>
-      </c>
-      <c r="C8" s="54" t="n">
-        <v>137.3595329507266</v>
+        <v>145.6558590377066</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>140.6020609136717</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>132.6858532590249</v>
+        <v>135.7827478868779</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>128.2273471874711</v>
+        <v>131.1857711979195</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>123.9729360998677</v>
+        <v>126.7996696154209</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>119.9121648438594</v>
+        <v>122.6136274326815</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>116.0351638575154</v>
+        <v>118.6174352128938</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="53" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>149.0515891472821</v>
+        <v>152.4473192568577</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>143.8445888766169</v>
+        <v>147.087116839562</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>138.8796425147309</v>
+        <v>141.9765371425839</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>134.144195208368</v>
+        <v>137.1026192188164</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>129.626403130974</v>
+        <v>132.4531366465272</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>125.3150900215037</v>
+        <v>128.0165526103258</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>121.1997065682723</v>
+        <v>123.7819779236508</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="53" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>155.8430493664333</v>
+        <v>159.2387794760089</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>150.3296448025071</v>
+        <v>153.5721727654522</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>145.0734317704369</v>
+        <v>148.17032639829</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>140.0610432292649</v>
+        <v>143.0194672397134</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>135.2798701620804</v>
+        <v>138.1066036776336</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>130.718015199148</v>
+        <v>133.4194777879701</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>126.3642492790293</v>
+        <v>128.9465206344077</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="53" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>162.6345095855845</v>
+        <v>166.03023969516</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>156.8147007283973</v>
+        <v>160.0572286913424</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>151.267221026143</v>
+        <v>154.364115653996</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>145.9778912501618</v>
+        <v>148.9363152606103</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>140.9333371931868</v>
+        <v>143.76007070874</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>136.1209403767923</v>
+        <v>138.8224029656145</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>131.5287919897862</v>
+        <v>134.1110633451646</v>
       </c>
     </row>
     <row r="13">
@@ -1328,7 +1328,7 @@
         <v>0.09556105229481747</v>
       </c>
       <c r="C14" s="57" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
     </row>
   </sheetData>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.8670131373774023</v>
+        <v>0.865797111569466</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24375,7 +24375,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="46">
@@ -24572,13 +24572,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>128.2273471874711</v>
+        <v>131.1857711979195</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>170.8089626061391</v>
+        <v>174.5657899073667</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>96.36021098023213</v>
+        <v>98.67351125131489</v>
       </c>
     </row>
     <row r="59">

--- a/dcf/ABNB.xlsx
+++ b/dcf/ABNB.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
